--- a/data/evalutation/EvaluationTable.xlsx
+++ b/data/evalutation/EvaluationTable.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jatinarora/Desktop/University/Natural Language Processing/CarbonAccountingChatbot/data/evalutation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{42849097-CCF8-794F-BBF9-349EA0A701EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71D79773-1091-664F-A750-F48BAB0B5D08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10280" yWindow="780" windowWidth="25720" windowHeight="22600" xr2:uid="{B0263151-7B99-FE44-98E9-A1522D193AEF}"/>
+    <workbookView xWindow="10280" yWindow="600" windowWidth="25720" windowHeight="21000" xr2:uid="{B0263151-7B99-FE44-98E9-A1522D193AEF}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="69">
   <si>
     <t>Metric</t>
   </si>
@@ -81,6 +82,168 @@
   </si>
   <si>
     <t>BART/T5</t>
+  </si>
+  <si>
+    <t>≥ 85%</t>
+  </si>
+  <si>
+    <t>≥ 70%</t>
+  </si>
+  <si>
+    <t>15.95s</t>
+  </si>
+  <si>
+    <t>&lt; 2s</t>
+  </si>
+  <si>
+    <t>≥ 0.8</t>
+  </si>
+  <si>
+    <t>GPT-5.2</t>
+  </si>
+  <si>
+    <t>GPT-5.3</t>
+  </si>
+  <si>
+    <t>GPT-5.4</t>
+  </si>
+  <si>
+    <t>GPT-5.5</t>
+  </si>
+  <si>
+    <t>GPT-5.6</t>
+  </si>
+  <si>
+    <t>#</t>
+  </si>
+  <si>
+    <t>Question (truncated)</t>
+  </si>
+  <si>
+    <t>SC</t>
+  </si>
+  <si>
+    <t>F1</t>
+  </si>
+  <si>
+    <t>Latency (s)</t>
+  </si>
+  <si>
+    <t>Which organizations fall under the manda...</t>
+  </si>
+  <si>
+    <t>What is the 'base year' in carbon accoun...</t>
+  </si>
+  <si>
+    <t>Are UK unquoted companies required to re...</t>
+  </si>
+  <si>
+    <t>What are the specific requirements for r...</t>
+  </si>
+  <si>
+    <t>How should an organization report 'bioge...</t>
+  </si>
+  <si>
+    <t>What is the primary difference between '...</t>
+  </si>
+  <si>
+    <t>Define Scope 3 Category 1 emissions (Pur...</t>
+  </si>
+  <si>
+    <t>Under what circumstances does the GHG Pr...</t>
+  </si>
+  <si>
+    <t>Does the GHG Protocol Corporate Standard...</t>
+  </si>
+  <si>
+    <t>What is a 'consolidated GHG inventory,' ...</t>
+  </si>
+  <si>
+    <t>What were the primary changes introduced...</t>
+  </si>
+  <si>
+    <t>According to ISO 14064-1:2018, what are ...</t>
+  </si>
+  <si>
+    <t>How does ISO 14064-1:2018 define 'direct...</t>
+  </si>
+  <si>
+    <t>What are the requirements for an 'intern...</t>
+  </si>
+  <si>
+    <t>Which specific industrial sectors are cu...</t>
+  </si>
+  <si>
+    <t>What is the 2024 UK government (DEFRA) c...</t>
+  </si>
+  <si>
+    <t>How should 'well-to-tank' (WTT) emission...</t>
+  </si>
+  <si>
+    <t>What is a 'Global Warming Potential' (GW...</t>
+  </si>
+  <si>
+    <t>How do you calculate Scope 1 emissions f...</t>
+  </si>
+  <si>
+    <t>What are 'fugitive emissions,' and which...</t>
+  </si>
+  <si>
+    <t>BART/T6</t>
+  </si>
+  <si>
+    <t>BART/T7</t>
+  </si>
+  <si>
+    <t>BART/T8</t>
+  </si>
+  <si>
+    <t>BART/T9</t>
+  </si>
+  <si>
+    <t>BART/T10</t>
+  </si>
+  <si>
+    <t>BART/T11</t>
+  </si>
+  <si>
+    <t>BART/T12</t>
+  </si>
+  <si>
+    <t>BART/T13</t>
+  </si>
+  <si>
+    <t>BART/T14</t>
+  </si>
+  <si>
+    <t>BART/T15</t>
+  </si>
+  <si>
+    <t>BART/T16</t>
+  </si>
+  <si>
+    <t>BART/T17</t>
+  </si>
+  <si>
+    <t>BART/T18</t>
+  </si>
+  <si>
+    <t>BART/T19</t>
+  </si>
+  <si>
+    <t>BART/T20</t>
+  </si>
+  <si>
+    <t>BART/T21</t>
+  </si>
+  <si>
+    <t>BART/T22</t>
+  </si>
+  <si>
+    <t>BART/T23</t>
+  </si>
+  <si>
+    <t>BART/T24</t>
   </si>
 </sst>
 </file>
@@ -483,9 +646,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2ED1CCDB-4299-B046-93D1-90C00648E316}">
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
+    <col min="1" max="1" width="7.83203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="27.1640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="8.1640625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="7.33203125" bestFit="1" customWidth="1"/>
@@ -575,6 +739,913 @@
         <v>12</v>
       </c>
     </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C7" s="3">
+        <v>0.65400000000000003</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8" s="3">
+        <v>0.27279999999999999</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>22</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" s="3">
+        <v>0</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>23</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="3">
+        <v>0.6</v>
+      </c>
+      <c r="D10" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>24</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2028EB9-3AEB-0941-9487-13FF884AB993}">
+  <dimension ref="A1:F41"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="3.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="43.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="5.83203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.83203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B2" s="2">
+        <v>1</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D2" s="2">
+        <v>0.81</v>
+      </c>
+      <c r="E2" s="2">
+        <v>0.48</v>
+      </c>
+      <c r="F2" s="2">
+        <v>15.26</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B3" s="2">
+        <v>2</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D3" s="2">
+        <v>0.74</v>
+      </c>
+      <c r="E3" s="2">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="F3" s="2">
+        <v>17.059999999999999</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B4" s="2">
+        <v>3</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D4" s="2">
+        <v>0.8</v>
+      </c>
+      <c r="E4" s="2">
+        <v>0.46</v>
+      </c>
+      <c r="F4" s="2">
+        <v>8.99</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" s="2">
+        <v>4</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D5" s="2">
+        <v>0.72</v>
+      </c>
+      <c r="E5" s="2">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="F5" s="2">
+        <v>17.91</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="2">
+        <v>5</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D6" s="2">
+        <v>0.71</v>
+      </c>
+      <c r="E6" s="2">
+        <v>0.19</v>
+      </c>
+      <c r="F6" s="2">
+        <v>20.5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7" s="2">
+        <v>6</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D7" s="2">
+        <v>0.74</v>
+      </c>
+      <c r="E7" s="2">
+        <v>0.36</v>
+      </c>
+      <c r="F7" s="2">
+        <v>6.72</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8" s="2">
+        <v>7</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D8" s="2">
+        <v>0.79</v>
+      </c>
+      <c r="E8" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="F8" s="2">
+        <v>14.37</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>20</v>
+      </c>
+      <c r="B9" s="2">
+        <v>8</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D9" s="2">
+        <v>0.73</v>
+      </c>
+      <c r="E9" s="2">
+        <v>0.34</v>
+      </c>
+      <c r="F9" s="2">
+        <v>7.51</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>20</v>
+      </c>
+      <c r="B10" s="2">
+        <v>9</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D10" s="2">
+        <v>0.81</v>
+      </c>
+      <c r="E10" s="2">
+        <v>0.4</v>
+      </c>
+      <c r="F10" s="2">
+        <v>13.47</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11" s="2">
+        <v>10</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D11" s="2">
+        <v>0.87</v>
+      </c>
+      <c r="E11" s="2">
+        <v>0.46</v>
+      </c>
+      <c r="F11" s="2">
+        <v>19.23</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>20</v>
+      </c>
+      <c r="B12" s="2">
+        <v>11</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D12" s="2">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="E12" s="2">
+        <v>0.03</v>
+      </c>
+      <c r="F12" s="2">
+        <v>20.02</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>20</v>
+      </c>
+      <c r="B13" s="2">
+        <v>12</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D13" s="2">
+        <v>0.62</v>
+      </c>
+      <c r="E13" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="F13" s="2">
+        <v>21.15</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>20</v>
+      </c>
+      <c r="B14" s="2">
+        <v>13</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D14" s="2">
+        <v>0.88</v>
+      </c>
+      <c r="E14" s="2">
+        <v>0.23</v>
+      </c>
+      <c r="F14" s="2">
+        <v>22.02</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>20</v>
+      </c>
+      <c r="B15" s="2">
+        <v>14</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D15" s="2">
+        <v>0.17</v>
+      </c>
+      <c r="E15" s="2">
+        <v>0.03</v>
+      </c>
+      <c r="F15" s="2">
+        <v>15.87</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>20</v>
+      </c>
+      <c r="B16" s="2">
+        <v>15</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D16" s="2">
+        <v>0.15</v>
+      </c>
+      <c r="E16" s="2">
+        <v>0.04</v>
+      </c>
+      <c r="F16" s="2">
+        <v>15.6</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>20</v>
+      </c>
+      <c r="B17" s="2">
+        <v>16</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D17" s="2">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="E17" s="2">
+        <v>0</v>
+      </c>
+      <c r="F17" s="2">
+        <v>12.32</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>20</v>
+      </c>
+      <c r="B18" s="2">
+        <v>17</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D18" s="2">
+        <v>0.84</v>
+      </c>
+      <c r="E18" s="2">
+        <v>0.24</v>
+      </c>
+      <c r="F18" s="2">
+        <v>6.67</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>20</v>
+      </c>
+      <c r="B19" s="2">
+        <v>18</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D19" s="2">
+        <v>0.85</v>
+      </c>
+      <c r="E19" s="2">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="F19" s="2">
+        <v>15.7</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>20</v>
+      </c>
+      <c r="B20" s="2">
+        <v>19</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D20" s="2">
+        <v>0.7</v>
+      </c>
+      <c r="E20" s="2">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="F20" s="2">
+        <v>30.51</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>20</v>
+      </c>
+      <c r="B21" s="2">
+        <v>20</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D21" s="2">
+        <v>0.85</v>
+      </c>
+      <c r="E21" s="2">
+        <v>0.4</v>
+      </c>
+      <c r="F21" s="2">
+        <v>18.03</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>14</v>
+      </c>
+      <c r="B22" s="2">
+        <v>1</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D22" s="2">
+        <v>0.69</v>
+      </c>
+      <c r="E22" s="2">
+        <v>0.35</v>
+      </c>
+      <c r="F22" s="2">
+        <v>2.74</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>50</v>
+      </c>
+      <c r="B23" s="2">
+        <v>2</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D23" s="2">
+        <v>0.34</v>
+      </c>
+      <c r="E23" s="2">
+        <v>0.09</v>
+      </c>
+      <c r="F23" s="2">
+        <v>1.22</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>51</v>
+      </c>
+      <c r="B24" s="2">
+        <v>3</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D24" s="2">
+        <v>0.46</v>
+      </c>
+      <c r="E24" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="F24" s="2">
+        <v>1.1599999999999999</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>52</v>
+      </c>
+      <c r="B25" s="2">
+        <v>4</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D25" s="2">
+        <v>0.73</v>
+      </c>
+      <c r="E25" s="2">
+        <v>0.23</v>
+      </c>
+      <c r="F25" s="2">
+        <v>1.1299999999999999</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
+        <v>53</v>
+      </c>
+      <c r="B26" s="2">
+        <v>5</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D26" s="2">
+        <v>0.53</v>
+      </c>
+      <c r="E26" s="2">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="F26" s="2">
+        <v>1.92</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
+        <v>54</v>
+      </c>
+      <c r="B27" s="2">
+        <v>6</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D27" s="2">
+        <v>0.64</v>
+      </c>
+      <c r="E27" s="2">
+        <v>0.21</v>
+      </c>
+      <c r="F27" s="2">
+        <v>2.46</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
+        <v>55</v>
+      </c>
+      <c r="B28" s="2">
+        <v>7</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D28" s="2">
+        <v>0.84</v>
+      </c>
+      <c r="E28" s="2">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="F28" s="2">
+        <v>1.01</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
+        <v>56</v>
+      </c>
+      <c r="B29" s="2">
+        <v>8</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D29" s="2">
+        <v>0.32</v>
+      </c>
+      <c r="E29" s="2">
+        <v>0.17</v>
+      </c>
+      <c r="F29" s="2">
+        <v>0.86</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
+        <v>57</v>
+      </c>
+      <c r="B30" s="2">
+        <v>9</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D30" s="2">
+        <v>0.78</v>
+      </c>
+      <c r="E30" s="2">
+        <v>0.38</v>
+      </c>
+      <c r="F30" s="2">
+        <v>1.21</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
+        <v>58</v>
+      </c>
+      <c r="B31" s="2">
+        <v>10</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D31" s="2">
+        <v>0.84</v>
+      </c>
+      <c r="E31" s="2">
+        <v>0.21</v>
+      </c>
+      <c r="F31" s="2">
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A32" t="s">
+        <v>59</v>
+      </c>
+      <c r="B32" s="2">
+        <v>11</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D32" s="2">
+        <v>0.19</v>
+      </c>
+      <c r="E32" s="2">
+        <v>0.13</v>
+      </c>
+      <c r="F32" s="2">
+        <v>0.92</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A33" t="s">
+        <v>60</v>
+      </c>
+      <c r="B33" s="2">
+        <v>12</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D33" s="2">
+        <v>0.65</v>
+      </c>
+      <c r="E33" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="F33" s="2">
+        <v>1.1399999999999999</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A34" t="s">
+        <v>61</v>
+      </c>
+      <c r="B34" s="2">
+        <v>13</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D34" s="2">
+        <v>0.88</v>
+      </c>
+      <c r="E34" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="F34" s="2">
+        <v>0.84</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A35" t="s">
+        <v>62</v>
+      </c>
+      <c r="B35" s="2">
+        <v>14</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D35" s="2">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="E35" s="2">
+        <v>0.06</v>
+      </c>
+      <c r="F35" s="2">
+        <v>0.96</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A36" t="s">
+        <v>63</v>
+      </c>
+      <c r="B36" s="2">
+        <v>15</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D36" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="E36" s="2">
+        <v>0.04</v>
+      </c>
+      <c r="F36" s="2">
+        <v>1.1299999999999999</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A37" t="s">
+        <v>64</v>
+      </c>
+      <c r="B37" s="2">
+        <v>16</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D37" s="2">
+        <v>0.18</v>
+      </c>
+      <c r="E37" s="2">
+        <v>0.03</v>
+      </c>
+      <c r="F37" s="2">
+        <v>1.86</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A38" t="s">
+        <v>65</v>
+      </c>
+      <c r="B38" s="2">
+        <v>17</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D38" s="2">
+        <v>0.74</v>
+      </c>
+      <c r="E38" s="2">
+        <v>0.34</v>
+      </c>
+      <c r="F38" s="2">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A39" t="s">
+        <v>66</v>
+      </c>
+      <c r="B39" s="2">
+        <v>18</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D39" s="2">
+        <v>0.79</v>
+      </c>
+      <c r="E39" s="2">
+        <v>0.18</v>
+      </c>
+      <c r="F39" s="2">
+        <v>1.26</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A40" t="s">
+        <v>67</v>
+      </c>
+      <c r="B40" s="2">
+        <v>19</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D40" s="2">
+        <v>0.54</v>
+      </c>
+      <c r="E40" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="F40" s="2">
+        <v>1.1100000000000001</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A41" t="s">
+        <v>68</v>
+      </c>
+      <c r="B41" s="2">
+        <v>20</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D41" s="2">
+        <v>0.71</v>
+      </c>
+      <c r="E41" s="2">
+        <v>0.26</v>
+      </c>
+      <c r="F41" s="2">
+        <v>1.19</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
